--- a/Design/Excel/ET/Datas/__beans__.xlsx
+++ b/Design/Excel/ET/Datas/__beans__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F411133-5672-4D67-B48A-13AA4F6C3DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38471A67-C364-4641-916B-0E7BA4E7567B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -134,6 +134,9 @@
   <si>
     <t>字段变体</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s,e</t>
   </si>
 </sst>
 </file>
@@ -632,6 +635,9 @@
       <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
       <c r="J4" s="2" t="s">
         <v>23</v>
       </c>
@@ -648,6 +654,7 @@
       <c r="L5" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="M5" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
